--- a/sheets/조재수대금교본/검수/쑥대머리.xlsx
+++ b/sheets/조재수대금교본/검수/쑥대머리.xlsx
@@ -6528,16 +6528,14 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
-潢
-ﾉ</t>
+          <t xml:space="preserve">南
+潢</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -6549,14 +6547,13 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∨
+          <t xml:space="preserve">汰
 △</t>
         </is>
       </c>
@@ -6570,7 +6567,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -6584,9 +6581,7 @@
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南
-ﾉ
-‹</t>
+南</t>
         </is>
       </c>
       <c r="G4" s="23"/>
@@ -6612,8 +6607,7 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
@@ -6639,24 +6633,18 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰南ㄴ
+          <t xml:space="preserve">汰南
 –</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-ﾉ
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M5" s="24"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
@@ -6665,13 +6653,7 @@
         </is>
       </c>
       <c r="Q5" s="24"/>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-ㄴ
-‹</t>
-        </is>
-      </c>
+      <c r="R5" s="21"/>
       <c r="S5" s="24"/>
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
@@ -6684,18 +6666,13 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -6705,10 +6682,8 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㳞汰c
-潢
-ﾉ
-‹</t>
+          <t xml:space="preserve">㳞汰
+潢</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -6717,15 +6692,14 @@
       <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰∼
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕淋
-汰∼
-‹</t>
+汰∼</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -6782,56 +6756,36 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南ﾉ</t>
+南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南ﾉ
-‹</t>
+南</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="S8" s="24"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="157.03" customHeight="true">
@@ -6843,21 +6797,19 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-太
-‹</t>
+太</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
+          <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
@@ -6865,7 +6817,6 @@
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-ﾉ
 △</t>
         </is>
       </c>
@@ -6890,7 +6841,7 @@
       <c r="S9" s="22"/>
       <c r="T9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="U9" s="22"/>
@@ -6903,8 +6854,7 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -6917,37 +6867,32 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-ﾉ
 △</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="S10" s="23"/>
@@ -6966,11 +6911,7 @@
         </is>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="24"/>
       <c r="J11" s="21"/>
       <c r="K11" s="24"/>
@@ -6994,15 +6935,13 @@
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="S11" s="24"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="U11" s="24"/>
@@ -7013,42 +6952,26 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21"/>
       <c r="E12" s="22"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F12" s="21"/>
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㳞汰
+          <t xml:space="preserve">㳞汰
 –∼</t>
         </is>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K12" s="22"/>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L12" s="21"/>
       <c r="M12" s="22"/>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N12" s="21"/>
       <c r="O12" s="22"/>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
@@ -7099,36 +7022,15 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
@@ -7180,8 +7082,8 @@
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c·
-汰c·</t>
+          <t xml:space="preserve">汰·
+汰·</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -7213,7 +7115,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
+          <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
@@ -7227,9 +7129,8 @@
       <c r="S17" s="22"/>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
-潢
-ﾉ</t>
+          <t xml:space="preserve">南
+潢</t>
         </is>
       </c>
       <c r="U17" s="22"/>
@@ -7240,16 +7141,11 @@
       <c r="C18" s="23"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="E18" s="23"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="23"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
@@ -7258,28 +7154,15 @@
         </is>
       </c>
       <c r="I18" s="23"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="23"/>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L18" s="21"/>
       <c r="M18" s="23"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="23"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-ﾉ
 △</t>
         </is>
       </c>
@@ -7295,11 +7178,7 @@
     </row>
     <row r="19" ht="157.03" customHeight="true">
       <c r="A19" s="0"/>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B19" s="21"/>
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
@@ -7310,7 +7189,7 @@
       <c r="E19" s="24"/>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c汰汰c
+          <t xml:space="preserve">汰汰
 淋</t>
         </is>
       </c>
@@ -7325,8 +7204,7 @@
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∼
-‹</t>
+          <t xml:space="preserve">淋∼</t>
         </is>
       </c>
       <c r="M19" s="24"/>
@@ -7339,15 +7217,11 @@
       <c r="O19" s="24"/>
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
-      <c r="R19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R19" s="21"/>
       <c r="S19" s="24"/>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="U19" s="24"/>
@@ -7366,7 +7240,7 @@
       <c r="G20" s="22"/>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㳞汰
+          <t xml:space="preserve">㳞汰
 –∼</t>
         </is>
       </c>
@@ -7384,7 +7258,7 @@
       <c r="O20" s="22"/>
       <c r="P20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q20" s="22"/>
@@ -7394,11 +7268,7 @@
         </is>
       </c>
       <c r="S20" s="22"/>
-      <c r="T20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
     <row r="21" ht="157.03" customHeight="true">
@@ -7437,31 +7307,17 @@
       <c r="B22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南
-ﾉ
-‹</t>
+南</t>
         </is>
       </c>
       <c r="C22" s="24"/>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D22" s="21"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F22" s="21"/>
       <c r="G22" s="24"/>
       <c r="H22" s="21"/>
       <c r="I22" s="24"/>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J22" s="21"/>
       <c r="K22" s="24"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
@@ -7469,32 +7325,17 @@
         </is>
       </c>
       <c r="M22" s="24"/>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N22" s="21"/>
       <c r="O22" s="24"/>
-      <c r="P22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
       <c r="R22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="S22" s="24"/>
-      <c r="T22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="T22" s="21"/>
       <c r="U22" s="24"/>
     </row>
     <row r="23" ht="157.03" customHeight="true">
@@ -7502,7 +7343,6 @@
       <c r="B23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-ﾉ
 △</t>
         </is>
       </c>
@@ -7523,7 +7363,7 @@
       <c r="H23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南ﾉ</t>
+南</t>
         </is>
       </c>
       <c r="I23" s="22"/>
@@ -7532,7 +7372,6 @@
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰南
-ﾉ
 △</t>
         </is>
       </c>
@@ -7540,7 +7379,6 @@
       <c r="N23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 汰</t>
         </is>
       </c>
@@ -7548,7 +7386,6 @@
       <c r="P23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 汰</t>
         </is>
       </c>
@@ -7556,7 +7393,6 @@
       <c r="R23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 林</t>
         </is>
       </c>
@@ -7564,8 +7400,7 @@
       <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南
-ﾉ</t>
+南</t>
         </is>
       </c>
       <c r="U23" s="22"/>
@@ -7574,18 +7409,13 @@
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="C24" s="23"/>
       <c r="D24" s="21"/>
       <c r="E24" s="23"/>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F24" s="21"/>
       <c r="G24" s="23"/>
       <c r="H24" s="21" t="inlineStr">
         <is>
@@ -7601,8 +7431,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="M24" s="23"/>
@@ -7614,11 +7443,7 @@
         </is>
       </c>
       <c r="Q24" s="23"/>
-      <c r="R24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R24" s="21"/>
       <c r="S24" s="23"/>
       <c r="T24" s="21" t="inlineStr">
         <is>
@@ -7645,11 +7470,7 @@
       <c r="G25" s="24"/>
       <c r="H25" s="21"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J25" s="21"/>
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
@@ -7657,11 +7478,7 @@
         </is>
       </c>
       <c r="M25" s="24"/>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N25" s="21"/>
       <c r="O25" s="24"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="24"/>
@@ -7671,55 +7488,41 @@
         </is>
       </c>
       <c r="S25" s="24"/>
-      <c r="T25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
     <row r="26" ht="157.03" customHeight="true">
       <c r="A26" s="0"/>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B26" s="21"/>
       <c r="C26" s="22"/>
       <c r="D26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ﾉ
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G26" s="22"/>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞c
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
       <c r="I26" s="22"/>
       <c r="J26" s="21"/>
       <c r="K26" s="22"/>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L26" s="21"/>
       <c r="M26" s="22"/>
       <c r="N26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-⊏∼
+∼
 –</t>
         </is>
       </c>
@@ -7727,21 +7530,15 @@
       <c r="P26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 汰</t>
         </is>
       </c>
       <c r="Q26" s="22"/>
-      <c r="R26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R26" s="21"/>
       <c r="S26" s="22"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∼
-‹</t>
+          <t xml:space="preserve">淋∼</t>
         </is>
       </c>
       <c r="U26" s="22"/>
@@ -7752,16 +7549,14 @@
       <c r="C27" s="23"/>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-c㳞汰c
-‹</t>
+㳞汰</t>
         </is>
       </c>
       <c r="G27" s="23"/>
@@ -7784,8 +7579,8 @@
       <c r="O27" s="23"/>
       <c r="P27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ﾉ
-c汰汰c</t>
+          <t xml:space="preserve">南
+汰汰</t>
         </is>
       </c>
       <c r="Q27" s="23"/>
@@ -7809,25 +7604,19 @@
       <c r="C28" s="24"/>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E28" s="24"/>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="G28" s="24"/>
       <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
       <c r="L28" s="21" t="inlineStr">
         <is>
@@ -7838,28 +7627,21 @@
       <c r="M28" s="24"/>
       <c r="N28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="O28" s="24"/>
       <c r="P28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="Q28" s="24"/>
-      <c r="R28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R28" s="21"/>
       <c r="S28" s="24"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="U28" s="24"/>

--- a/sheets/조재수대금교본/검수/쑥대머리.xlsx
+++ b/sheets/조재수대금교본/검수/쑥대머리.xlsx
@@ -6534,8 +6534,9 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-潢</t>
+          <t xml:space="preserve">南ㄴ
+潢
+ﾉ</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -6553,7 +6554,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∨
 △</t>
         </is>
       </c>
@@ -6567,7 +6568,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -6581,7 +6582,8 @@
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南</t>
+南
+ﾉ</t>
         </is>
       </c>
       <c r="G4" s="23"/>
@@ -6633,14 +6635,15 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰南
+          <t xml:space="preserve">汰南ㄴ
 –</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+ﾉ</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -6653,7 +6656,12 @@
         </is>
       </c>
       <c r="Q5" s="24"/>
-      <c r="R5" s="21"/>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ
+ㄴ</t>
+        </is>
+      </c>
       <c r="S5" s="24"/>
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
@@ -6672,7 +6680,11 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
-      <c r="J6" s="21"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -6682,8 +6694,9 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰
-潢</t>
+          <t xml:space="preserve">c㳞汰c
+潢
+ﾉ</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -6692,7 +6705,7 @@
       <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰∼
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S6" s="22"/>
@@ -6756,18 +6769,22 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南</t>
+南ﾉ</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南</t>
+南ﾉ</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -6809,7 +6826,7 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南ㄴ
 潢</t>
         </is>
       </c>
@@ -6817,6 +6834,7 @@
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
+ﾉ
 △</t>
         </is>
       </c>
@@ -6841,7 +6859,7 @@
       <c r="S9" s="22"/>
       <c r="T9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱㄴ</t>
         </is>
       </c>
       <c r="U9" s="22"/>
@@ -6867,6 +6885,7 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
+ﾉ
 △</t>
         </is>
       </c>
@@ -6941,7 +6960,7 @@
       <c r="S11" s="24"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∼</t>
         </is>
       </c>
       <c r="U11" s="24"/>
@@ -6952,26 +6971,42 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21"/>
       <c r="E12" s="22"/>
-      <c r="F12" s="21"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰
+          <t xml:space="preserve">c㳞汰
 –∼</t>
         </is>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="K12" s="22"/>
-      <c r="L12" s="21"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M12" s="22"/>
-      <c r="N12" s="21"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O12" s="22"/>
-      <c r="P12" s="21"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q12" s="22"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
@@ -7024,7 +7059,11 @@
       <c r="G14" s="24"/>
       <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K14" s="24"/>
       <c r="L14" s="21"/>
       <c r="M14" s="24"/>
@@ -7082,8 +7121,8 @@
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰·
-汰·</t>
+          <t xml:space="preserve">汰c·
+汰c·</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -7115,7 +7154,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南ㄴ
 潢</t>
         </is>
       </c>
@@ -7129,8 +7168,9 @@
       <c r="S17" s="22"/>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-潢</t>
+          <t xml:space="preserve">南ㄴ
+潢
+ﾉ</t>
         </is>
       </c>
       <c r="U17" s="22"/>
@@ -7163,6 +7203,7 @@
       <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
+ﾉ
 △</t>
         </is>
       </c>
@@ -7189,7 +7230,7 @@
       <c r="E19" s="24"/>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰汰
+          <t xml:space="preserve">c汰汰c
 淋</t>
         </is>
       </c>
@@ -7221,7 +7262,7 @@
       <c r="S19" s="24"/>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="U19" s="24"/>
@@ -7240,7 +7281,7 @@
       <c r="G20" s="22"/>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰
+          <t xml:space="preserve">c㳞汰
 –∼</t>
         </is>
       </c>
@@ -7258,7 +7299,7 @@
       <c r="O20" s="22"/>
       <c r="P20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="Q20" s="22"/>
@@ -7268,7 +7309,11 @@
         </is>
       </c>
       <c r="S20" s="22"/>
-      <c r="T20" s="21"/>
+      <c r="T20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U20" s="22"/>
     </row>
     <row r="21" ht="157.03" customHeight="true">
@@ -7307,7 +7352,8 @@
       <c r="B22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南</t>
+南
+ﾉ</t>
         </is>
       </c>
       <c r="C22" s="24"/>
@@ -7327,7 +7373,11 @@
       <c r="M22" s="24"/>
       <c r="N22" s="21"/>
       <c r="O22" s="24"/>
-      <c r="P22" s="21"/>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="Q22" s="24"/>
       <c r="R22" s="21" t="inlineStr">
         <is>
@@ -7335,7 +7385,11 @@
         </is>
       </c>
       <c r="S22" s="24"/>
-      <c r="T22" s="21"/>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="U22" s="24"/>
     </row>
     <row r="23" ht="157.03" customHeight="true">
@@ -7343,6 +7397,7 @@
       <c r="B23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
+ﾉ
 △</t>
         </is>
       </c>
@@ -7363,7 +7418,7 @@
       <c r="H23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南</t>
+南ﾉ</t>
         </is>
       </c>
       <c r="I23" s="22"/>
@@ -7372,6 +7427,7 @@
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰南
+ﾉ
 △</t>
         </is>
       </c>
@@ -7379,6 +7435,7 @@
       <c r="N23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 汰</t>
         </is>
       </c>
@@ -7386,6 +7443,7 @@
       <c r="P23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 汰</t>
         </is>
       </c>
@@ -7393,6 +7451,7 @@
       <c r="R23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 林</t>
         </is>
       </c>
@@ -7400,7 +7459,8 @@
       <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南</t>
+南
+ﾉ</t>
         </is>
       </c>
       <c r="U23" s="22"/>
@@ -7493,12 +7553,16 @@
     </row>
     <row r="26" ht="157.03" customHeight="true">
       <c r="A26" s="0"/>
-      <c r="B26" s="21"/>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C26" s="22"/>
       <c r="D26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ﾉ</t>
         </is>
       </c>
       <c r="E26" s="22"/>
@@ -7510,19 +7574,23 @@
       <c r="G26" s="22"/>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞c
 汰</t>
         </is>
       </c>
       <c r="I26" s="22"/>
       <c r="J26" s="21"/>
       <c r="K26" s="22"/>
-      <c r="L26" s="21"/>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M26" s="22"/>
       <c r="N26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-∼
+⊏∼
 –</t>
         </is>
       </c>
@@ -7530,11 +7598,16 @@
       <c r="P26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 汰</t>
         </is>
       </c>
       <c r="Q26" s="22"/>
-      <c r="R26" s="21"/>
+      <c r="R26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S26" s="22"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
@@ -7556,7 +7629,7 @@
       <c r="F27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞汰</t>
+c㳞汰c</t>
         </is>
       </c>
       <c r="G27" s="23"/>
@@ -7579,8 +7652,8 @@
       <c r="O27" s="23"/>
       <c r="P27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-汰汰</t>
+          <t xml:space="preserve">南ﾉ
+c汰汰c</t>
         </is>
       </c>
       <c r="Q27" s="23"/>

--- a/sheets/조재수대금교본/검수/쑥대머리.xlsx
+++ b/sheets/조재수대금교본/검수/쑥대머리.xlsx
@@ -6462,25 +6462,25 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="16.2" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="16.2" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
